--- a/data/2_keyword_profile/growth_tier_keyword_profile.xlsx
+++ b/data/2_keyword_profile/growth_tier_keyword_profile.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,7 +440,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3">
@@ -448,7 +448,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>156</v>
+        <v>386</v>
       </c>
     </row>
     <row r="4">
@@ -456,7 +456,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>201</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5">
@@ -464,7 +464,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>186</v>
+        <v>516</v>
       </c>
     </row>
     <row r="6">
@@ -472,7 +472,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>84</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
@@ -480,7 +480,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>126</v>
+        <v>320</v>
       </c>
     </row>
     <row r="8">
@@ -488,38 +488,6 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="n">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="n">
         <v>3282</v>
       </c>
     </row>
@@ -534,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N147"/>
+  <dimension ref="A1:J147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -585,26 +553,6 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Tier_8_Tier 8</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Tier_9_Tier 9</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Tier_10_Tier 10</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Tier_11_Tier 11</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
           <t>Total</t>
         </is>
       </c>
@@ -621,39 +569,27 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>159</v>
       </c>
       <c r="D2" t="n">
-        <v>159</v>
+        <v>595</v>
       </c>
       <c r="E2" t="n">
-        <v>403</v>
+        <v>202</v>
       </c>
       <c r="F2" t="n">
-        <v>194</v>
+        <v>110</v>
       </c>
       <c r="G2" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>126</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
         <v>1072</v>
       </c>
     </row>
@@ -672,36 +608,24 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>393</v>
       </c>
       <c r="E3" t="n">
-        <v>202</v>
+        <v>147</v>
       </c>
       <c r="F3" t="n">
-        <v>192</v>
+        <v>73</v>
       </c>
       <c r="G3" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>126</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>2</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
         <v>619</v>
       </c>
     </row>
@@ -717,39 +641,27 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" t="n">
         <v>3</v>
       </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
       <c r="F4" t="n">
+        <v>517</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>44</v>
+      </c>
+      <c r="I4" t="n">
         <v>5</v>
       </c>
-      <c r="G4" t="n">
-        <v>31</v>
-      </c>
-      <c r="H4" t="n">
-        <v>36</v>
-      </c>
-      <c r="I4" t="n">
-        <v>449</v>
-      </c>
       <c r="J4" t="n">
-        <v>39</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M4" t="n">
-        <v>5</v>
-      </c>
-      <c r="N4" t="n">
         <v>579</v>
       </c>
     </row>
@@ -765,39 +677,27 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>324</v>
       </c>
       <c r="I5" t="n">
         <v>5</v>
       </c>
       <c r="J5" t="n">
-        <v>39</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>283</v>
-      </c>
-      <c r="M5" t="n">
-        <v>5</v>
-      </c>
-      <c r="N5" t="n">
         <v>337</v>
       </c>
     </row>
@@ -816,36 +716,24 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
         <v>97</v>
       </c>
     </row>
@@ -864,36 +752,24 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
         <v>54</v>
       </c>
     </row>
@@ -912,36 +788,24 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>36</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
         <v>41</v>
       </c>
     </row>
@@ -960,36 +824,24 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>3</v>
-      </c>
-      <c r="M9" t="n">
-        <v>2</v>
-      </c>
-      <c r="N9" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1008,7 +860,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -1023,21 +875,9 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>6</v>
-      </c>
-      <c r="N10" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1071,21 +911,9 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>3</v>
-      </c>
-      <c r="N11" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1107,13 +935,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1122,18 +950,6 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1167,21 +983,9 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1197,39 +1001,27 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>5</v>
+        <v>110</v>
       </c>
       <c r="F14" t="n">
-        <v>7</v>
+        <v>186</v>
       </c>
       <c r="G14" t="n">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="I14" t="n">
-        <v>169</v>
+        <v>225</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>13</v>
-      </c>
-      <c r="L14" t="n">
-        <v>74</v>
-      </c>
-      <c r="M14" t="n">
-        <v>225</v>
-      </c>
-      <c r="N14" t="n">
         <v>619</v>
       </c>
     </row>
@@ -1248,36 +1040,24 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1308,24 +1088,12 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1356,24 +1124,12 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1392,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -1407,21 +1163,9 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1452,24 +1196,12 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1494,7 +1226,7 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1503,21 +1235,9 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1542,7 +1262,7 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1551,21 +1271,9 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1581,39 +1289,27 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F22" t="n">
+        <v>22</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" t="n">
         <v>6</v>
       </c>
-      <c r="G22" t="n">
-        <v>22</v>
-      </c>
-      <c r="H22" t="n">
-        <v>17</v>
-      </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2</v>
-      </c>
-      <c r="L22" t="n">
-        <v>6</v>
-      </c>
-      <c r="M22" t="n">
-        <v>11</v>
-      </c>
-      <c r="N22" t="n">
         <v>72</v>
       </c>
     </row>
@@ -1629,39 +1325,27 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="E23" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="F23" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="I23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
-        <v>3</v>
-      </c>
-      <c r="M23" t="n">
-        <v>9</v>
-      </c>
-      <c r="N23" t="n">
         <v>65</v>
       </c>
     </row>
@@ -1686,30 +1370,18 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>8</v>
-      </c>
-      <c r="M24" t="n">
-        <v>4</v>
-      </c>
-      <c r="N24" t="n">
         <v>14</v>
       </c>
     </row>
@@ -1728,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1743,21 +1415,9 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>5</v>
-      </c>
-      <c r="N25" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1779,33 +1439,21 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1836,24 +1484,12 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1887,21 +1523,9 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1</v>
-      </c>
-      <c r="N28" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1926,10 +1550,10 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1938,18 +1562,6 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1983,21 +1595,9 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1</v>
-      </c>
-      <c r="N30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2016,36 +1616,24 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="E31" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="F31" t="n">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="G31" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="I31" t="n">
-        <v>87</v>
+        <v>33</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>1</v>
-      </c>
-      <c r="L31" t="n">
-        <v>13</v>
-      </c>
-      <c r="M31" t="n">
-        <v>33</v>
-      </c>
-      <c r="N31" t="n">
         <v>251</v>
       </c>
     </row>
@@ -2067,33 +1655,21 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
         <v>74</v>
       </c>
     </row>
@@ -2112,36 +1688,24 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I33" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>2</v>
-      </c>
-      <c r="M33" t="n">
-        <v>9</v>
-      </c>
-      <c r="N33" t="n">
         <v>19</v>
       </c>
     </row>
@@ -2163,33 +1727,21 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
         <v>15</v>
       </c>
     </row>
@@ -2214,30 +1766,18 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>1</v>
-      </c>
-      <c r="M35" t="n">
-        <v>3</v>
-      </c>
-      <c r="N35" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2268,24 +1808,12 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>3</v>
-      </c>
-      <c r="M36" t="n">
-        <v>1</v>
-      </c>
-      <c r="N36" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2319,21 +1847,9 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>2</v>
-      </c>
-      <c r="N37" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2367,21 +1883,9 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>1</v>
-      </c>
-      <c r="N38" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2400,36 +1904,24 @@
         <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="E39" t="n">
-        <v>14</v>
+        <v>114</v>
       </c>
       <c r="F39" t="n">
-        <v>29</v>
+        <v>276</v>
       </c>
       <c r="G39" t="n">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="H39" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I39" t="n">
-        <v>226</v>
+        <v>196</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
-        <v>15</v>
-      </c>
-      <c r="L39" t="n">
-        <v>87</v>
-      </c>
-      <c r="M39" t="n">
-        <v>196</v>
-      </c>
-      <c r="N39" t="n">
         <v>735</v>
       </c>
     </row>
@@ -2445,39 +1937,27 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>118</v>
       </c>
       <c r="E40" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F40" t="n">
-        <v>101</v>
+        <v>227</v>
       </c>
       <c r="G40" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H40" t="n">
-        <v>60</v>
+        <v>98</v>
       </c>
       <c r="I40" t="n">
-        <v>184</v>
+        <v>98</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="n">
-        <v>13</v>
-      </c>
-      <c r="L40" t="n">
-        <v>96</v>
-      </c>
-      <c r="M40" t="n">
-        <v>98</v>
-      </c>
-      <c r="N40" t="n">
         <v>587</v>
       </c>
     </row>
@@ -2493,39 +1973,27 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="I41" t="n">
-        <v>86</v>
+        <v>5</v>
       </c>
       <c r="J41" t="n">
-        <v>39</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="n">
-        <v>11</v>
-      </c>
-      <c r="M41" t="n">
-        <v>5</v>
-      </c>
-      <c r="N41" t="n">
         <v>144</v>
       </c>
     </row>
@@ -2541,39 +2009,27 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="G42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H42" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="I42" t="n">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="n">
-        <v>6</v>
-      </c>
-      <c r="L42" t="n">
-        <v>20</v>
-      </c>
-      <c r="M42" t="n">
-        <v>13</v>
-      </c>
-      <c r="N42" t="n">
         <v>102</v>
       </c>
     </row>
@@ -2592,36 +2048,24 @@
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E43" t="n">
         <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="I43" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="n">
-        <v>1</v>
-      </c>
-      <c r="L43" t="n">
-        <v>18</v>
-      </c>
-      <c r="M43" t="n">
-        <v>43</v>
-      </c>
-      <c r="N43" t="n">
         <v>93</v>
       </c>
     </row>
@@ -2640,36 +2084,24 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F44" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H44" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I44" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="n">
-        <v>4</v>
-      </c>
-      <c r="L44" t="n">
-        <v>13</v>
-      </c>
-      <c r="M44" t="n">
-        <v>30</v>
-      </c>
-      <c r="N44" t="n">
         <v>90</v>
       </c>
     </row>
@@ -2694,30 +2126,18 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I45" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
-        <v>1</v>
-      </c>
-      <c r="L45" t="n">
-        <v>12</v>
-      </c>
-      <c r="M45" t="n">
-        <v>32</v>
-      </c>
-      <c r="N45" t="n">
         <v>55</v>
       </c>
     </row>
@@ -2736,36 +2156,24 @@
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I46" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
-        <v>3</v>
-      </c>
-      <c r="L46" t="n">
-        <v>7</v>
-      </c>
-      <c r="M46" t="n">
-        <v>7</v>
-      </c>
-      <c r="N46" t="n">
         <v>39</v>
       </c>
     </row>
@@ -2790,30 +2198,18 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
-        <v>3</v>
-      </c>
-      <c r="M47" t="n">
-        <v>8</v>
-      </c>
-      <c r="N47" t="n">
         <v>27</v>
       </c>
     </row>
@@ -2838,30 +2234,18 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>10</v>
-      </c>
-      <c r="M48" t="n">
-        <v>7</v>
-      </c>
-      <c r="N48" t="n">
         <v>20</v>
       </c>
     </row>
@@ -2877,39 +2261,27 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D49" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
-        <v>2</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="n">
         <v>15</v>
       </c>
     </row>
@@ -2934,30 +2306,18 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="n">
-        <v>1</v>
-      </c>
-      <c r="L50" t="n">
-        <v>3</v>
-      </c>
-      <c r="M50" t="n">
-        <v>8</v>
-      </c>
-      <c r="N50" t="n">
         <v>14</v>
       </c>
     </row>
@@ -2982,30 +2342,18 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I51" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
-        <v>5</v>
-      </c>
-      <c r="M51" t="n">
-        <v>4</v>
-      </c>
-      <c r="N51" t="n">
         <v>11</v>
       </c>
     </row>
@@ -3030,30 +2378,18 @@
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" t="n">
-        <v>3</v>
-      </c>
-      <c r="M52" t="n">
-        <v>3</v>
-      </c>
-      <c r="N52" t="n">
         <v>7</v>
       </c>
     </row>
@@ -3072,13 +2408,13 @@
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -3087,21 +2423,9 @@
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
         <v>7</v>
       </c>
     </row>
@@ -3126,7 +2450,7 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -3135,21 +2459,9 @@
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="n">
         <v>6</v>
       </c>
     </row>
@@ -3174,30 +2486,18 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I55" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
-        <v>3</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" t="n">
         <v>6</v>
       </c>
     </row>
@@ -3222,30 +2522,18 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" t="n">
-        <v>3</v>
-      </c>
-      <c r="M56" t="n">
-        <v>2</v>
-      </c>
-      <c r="N56" t="n">
         <v>6</v>
       </c>
     </row>
@@ -3273,27 +2561,15 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" t="n">
-        <v>1</v>
-      </c>
-      <c r="L57" t="n">
-        <v>1</v>
-      </c>
-      <c r="M57" t="n">
-        <v>4</v>
-      </c>
-      <c r="N57" t="n">
         <v>6</v>
       </c>
     </row>
@@ -3309,7 +2585,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D58" t="n">
         <v>1</v>
@@ -3318,7 +2594,7 @@
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -3330,18 +2606,6 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3360,7 +2624,7 @@
         <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
@@ -3375,21 +2639,9 @@
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3405,7 +2657,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D60" t="n">
         <v>1</v>
@@ -3414,7 +2666,7 @@
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -3426,18 +2678,6 @@
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3462,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -3474,18 +2714,6 @@
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3519,21 +2747,9 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" t="n">
-        <v>1</v>
-      </c>
-      <c r="N62" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3552,13 +2768,13 @@
         <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -3570,18 +2786,6 @@
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3606,7 +2810,7 @@
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -3615,21 +2819,9 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3654,7 +2846,7 @@
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -3663,21 +2855,9 @@
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" t="n">
-        <v>0</v>
-      </c>
-      <c r="N65" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3702,7 +2882,7 @@
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -3711,21 +2891,9 @@
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3750,7 +2918,7 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -3759,21 +2927,9 @@
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" t="n">
-        <v>0</v>
-      </c>
-      <c r="M67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N67" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3807,21 +2963,9 @@
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" t="n">
-        <v>1</v>
-      </c>
-      <c r="N68" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3855,21 +2999,9 @@
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" t="n">
-        <v>1</v>
-      </c>
-      <c r="N69" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3903,21 +3035,9 @@
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" t="n">
-        <v>1</v>
-      </c>
-      <c r="N70" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3951,21 +3071,9 @@
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" t="n">
-        <v>1</v>
-      </c>
-      <c r="N71" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3990,7 +3098,7 @@
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -3999,21 +3107,9 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" t="n">
-        <v>0</v>
-      </c>
-      <c r="N72" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4038,30 +3134,18 @@
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" t="n">
-        <v>2</v>
-      </c>
-      <c r="M73" t="n">
-        <v>2</v>
-      </c>
-      <c r="N73" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4092,24 +3176,12 @@
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
-      </c>
-      <c r="K74" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" t="n">
-        <v>4</v>
-      </c>
-      <c r="M74" t="n">
-        <v>1</v>
-      </c>
-      <c r="N74" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4134,7 +3206,7 @@
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -4143,21 +3215,9 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" t="n">
-        <v>0</v>
-      </c>
-      <c r="N75" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4188,24 +3248,12 @@
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" t="n">
-        <v>2</v>
-      </c>
-      <c r="M76" t="n">
-        <v>2</v>
-      </c>
-      <c r="N76" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4239,21 +3287,9 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" t="n">
-        <v>4</v>
-      </c>
-      <c r="N77" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4278,30 +3314,18 @@
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I78" t="n">
         <v>1</v>
       </c>
       <c r="J78" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" t="n">
-        <v>1</v>
-      </c>
-      <c r="M78" t="n">
-        <v>1</v>
-      </c>
-      <c r="N78" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4332,24 +3356,12 @@
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" t="n">
-        <v>2</v>
-      </c>
-      <c r="M79" t="n">
-        <v>0</v>
-      </c>
-      <c r="N79" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4380,24 +3392,12 @@
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" t="n">
-        <v>2</v>
-      </c>
-      <c r="M80" t="n">
-        <v>0</v>
-      </c>
-      <c r="N80" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4431,21 +3431,9 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J81" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" t="n">
-        <v>2</v>
-      </c>
-      <c r="N81" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4479,21 +3467,9 @@
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
-      </c>
-      <c r="K82" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" t="n">
-        <v>2</v>
-      </c>
-      <c r="N82" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4524,24 +3500,12 @@
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" t="n">
-        <v>1</v>
-      </c>
-      <c r="M83" t="n">
-        <v>1</v>
-      </c>
-      <c r="N83" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4575,21 +3539,9 @@
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J84" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" t="n">
-        <v>1</v>
-      </c>
-      <c r="N84" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4623,21 +3575,9 @@
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" t="n">
-        <v>1</v>
-      </c>
-      <c r="N85" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4662,7 +3602,7 @@
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -4671,21 +3611,9 @@
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>0</v>
-      </c>
-      <c r="K86" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" t="n">
-        <v>0</v>
-      </c>
-      <c r="N86" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4719,21 +3647,9 @@
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J87" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" t="n">
-        <v>0</v>
-      </c>
-      <c r="M87" t="n">
-        <v>1</v>
-      </c>
-      <c r="N87" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4758,7 +3674,7 @@
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -4767,21 +3683,9 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" t="n">
-        <v>0</v>
-      </c>
-      <c r="N88" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4815,21 +3719,9 @@
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
-        <v>0</v>
-      </c>
-      <c r="K89" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" t="n">
-        <v>0</v>
-      </c>
-      <c r="M89" t="n">
-        <v>1</v>
-      </c>
-      <c r="N89" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4854,7 +3746,7 @@
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -4863,21 +3755,9 @@
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4902,7 +3782,7 @@
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -4911,21 +3791,9 @@
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4956,24 +3824,12 @@
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" t="n">
-        <v>1</v>
-      </c>
-      <c r="M92" t="n">
-        <v>0</v>
-      </c>
-      <c r="N92" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5007,21 +3863,9 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
-        <v>0</v>
-      </c>
-      <c r="K93" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" t="n">
-        <v>0</v>
-      </c>
-      <c r="M93" t="n">
-        <v>1</v>
-      </c>
-      <c r="N93" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5055,21 +3899,9 @@
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
-      </c>
-      <c r="K94" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" t="n">
-        <v>0</v>
-      </c>
-      <c r="M94" t="n">
-        <v>1</v>
-      </c>
-      <c r="N94" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5100,24 +3932,12 @@
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>0</v>
-      </c>
-      <c r="K95" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" t="n">
-        <v>1</v>
-      </c>
-      <c r="M95" t="n">
-        <v>0</v>
-      </c>
-      <c r="N95" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5151,21 +3971,9 @@
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
-        <v>0</v>
-      </c>
-      <c r="K96" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" t="n">
-        <v>0</v>
-      </c>
-      <c r="M96" t="n">
-        <v>1</v>
-      </c>
-      <c r="N96" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5190,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -5202,18 +4010,6 @@
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>0</v>
-      </c>
-      <c r="K97" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" t="n">
-        <v>0</v>
-      </c>
-      <c r="M97" t="n">
-        <v>0</v>
-      </c>
-      <c r="N97" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5238,30 +4034,18 @@
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I98" t="n">
         <v>1</v>
       </c>
       <c r="J98" t="n">
-        <v>0</v>
-      </c>
-      <c r="K98" t="n">
-        <v>1</v>
-      </c>
-      <c r="L98" t="n">
-        <v>2</v>
-      </c>
-      <c r="M98" t="n">
-        <v>1</v>
-      </c>
-      <c r="N98" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5292,24 +4076,12 @@
         <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>0</v>
-      </c>
-      <c r="K99" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" t="n">
-        <v>4</v>
-      </c>
-      <c r="M99" t="n">
-        <v>0</v>
-      </c>
-      <c r="N99" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5334,30 +4106,18 @@
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>0</v>
-      </c>
-      <c r="K100" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" t="n">
-        <v>1</v>
-      </c>
-      <c r="M100" t="n">
-        <v>0</v>
-      </c>
-      <c r="N100" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5391,21 +4151,9 @@
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J101" t="n">
-        <v>0</v>
-      </c>
-      <c r="K101" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" t="n">
-        <v>0</v>
-      </c>
-      <c r="M101" t="n">
-        <v>2</v>
-      </c>
-      <c r="N101" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5436,24 +4184,12 @@
         <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I102" t="n">
         <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>0</v>
-      </c>
-      <c r="K102" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" t="n">
-        <v>2</v>
-      </c>
-      <c r="M102" t="n">
-        <v>0</v>
-      </c>
-      <c r="N102" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5487,21 +4223,9 @@
         <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J103" t="n">
-        <v>0</v>
-      </c>
-      <c r="K103" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" t="n">
-        <v>0</v>
-      </c>
-      <c r="M103" t="n">
-        <v>2</v>
-      </c>
-      <c r="N103" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5532,24 +4256,12 @@
         <v>0</v>
       </c>
       <c r="H104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I104" t="n">
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>0</v>
-      </c>
-      <c r="K104" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" t="n">
-        <v>1</v>
-      </c>
-      <c r="M104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N104" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5580,24 +4292,12 @@
         <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I105" t="n">
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>0</v>
-      </c>
-      <c r="K105" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" t="n">
-        <v>1</v>
-      </c>
-      <c r="M105" t="n">
-        <v>0</v>
-      </c>
-      <c r="N105" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5631,21 +4331,9 @@
         <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J106" t="n">
-        <v>0</v>
-      </c>
-      <c r="K106" t="n">
-        <v>0</v>
-      </c>
-      <c r="L106" t="n">
-        <v>0</v>
-      </c>
-      <c r="M106" t="n">
-        <v>1</v>
-      </c>
-      <c r="N106" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5661,39 +4349,27 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>5</v>
+        <v>162</v>
       </c>
       <c r="D107" t="n">
-        <v>162</v>
+        <v>406</v>
       </c>
       <c r="E107" t="n">
-        <v>205</v>
+        <v>150</v>
       </c>
       <c r="F107" t="n">
-        <v>202</v>
+        <v>550</v>
       </c>
       <c r="G107" t="n">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="H107" t="n">
-        <v>126</v>
+        <v>362</v>
       </c>
       <c r="I107" t="n">
-        <v>482</v>
+        <v>3369</v>
       </c>
       <c r="J107" t="n">
-        <v>39</v>
-      </c>
-      <c r="K107" t="n">
-        <v>40</v>
-      </c>
-      <c r="L107" t="n">
-        <v>321</v>
-      </c>
-      <c r="M107" t="n">
-        <v>3369</v>
-      </c>
-      <c r="N107" t="n">
         <v>5039</v>
       </c>
     </row>
@@ -5709,39 +4385,27 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>6</v>
+        <v>156</v>
       </c>
       <c r="D108" t="n">
-        <v>156</v>
+        <v>388</v>
       </c>
       <c r="E108" t="n">
-        <v>201</v>
+        <v>147</v>
       </c>
       <c r="F108" t="n">
-        <v>188</v>
+        <v>516</v>
       </c>
       <c r="G108" t="n">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="H108" t="n">
-        <v>126</v>
+        <v>321</v>
       </c>
       <c r="I108" t="n">
-        <v>448</v>
+        <v>3283</v>
       </c>
       <c r="J108" t="n">
-        <v>39</v>
-      </c>
-      <c r="K108" t="n">
-        <v>36</v>
-      </c>
-      <c r="L108" t="n">
-        <v>280</v>
-      </c>
-      <c r="M108" t="n">
-        <v>3283</v>
-      </c>
-      <c r="N108" t="n">
         <v>4847</v>
       </c>
     </row>
@@ -5757,39 +4421,27 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>5</v>
+        <v>157</v>
       </c>
       <c r="D109" t="n">
-        <v>157</v>
+        <v>387</v>
       </c>
       <c r="E109" t="n">
-        <v>201</v>
+        <v>146</v>
       </c>
       <c r="F109" t="n">
-        <v>187</v>
+        <v>514</v>
       </c>
       <c r="G109" t="n">
-        <v>83</v>
+        <v>30</v>
       </c>
       <c r="H109" t="n">
-        <v>125</v>
+        <v>309</v>
       </c>
       <c r="I109" t="n">
-        <v>447</v>
+        <v>3121</v>
       </c>
       <c r="J109" t="n">
-        <v>39</v>
-      </c>
-      <c r="K109" t="n">
-        <v>30</v>
-      </c>
-      <c r="L109" t="n">
-        <v>269</v>
-      </c>
-      <c r="M109" t="n">
-        <v>3121</v>
-      </c>
-      <c r="N109" t="n">
         <v>4664</v>
       </c>
     </row>
@@ -5805,39 +4457,27 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D110" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E110" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F110" t="n">
-        <v>8</v>
+        <v>630</v>
       </c>
       <c r="G110" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="H110" t="n">
-        <v>45</v>
+        <v>406</v>
       </c>
       <c r="I110" t="n">
-        <v>556</v>
+        <v>3400</v>
       </c>
       <c r="J110" t="n">
-        <v>78</v>
-      </c>
-      <c r="K110" t="n">
-        <v>41</v>
-      </c>
-      <c r="L110" t="n">
-        <v>326</v>
-      </c>
-      <c r="M110" t="n">
-        <v>3400</v>
-      </c>
-      <c r="N110" t="n">
         <v>4499</v>
       </c>
     </row>
@@ -5853,39 +4493,27 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D111" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E111" t="n">
         <v>1</v>
       </c>
       <c r="F111" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H111" t="n">
-        <v>1</v>
+        <v>244</v>
       </c>
       <c r="I111" t="n">
-        <v>9</v>
+        <v>3282</v>
       </c>
       <c r="J111" t="n">
-        <v>1</v>
-      </c>
-      <c r="K111" t="n">
-        <v>36</v>
-      </c>
-      <c r="L111" t="n">
-        <v>243</v>
-      </c>
-      <c r="M111" t="n">
-        <v>3282</v>
-      </c>
-      <c r="N111" t="n">
         <v>3576</v>
       </c>
     </row>
@@ -5904,36 +4532,24 @@
         <v>0</v>
       </c>
       <c r="D112" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E112" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H112" t="n">
-        <v>1</v>
+        <v>135</v>
       </c>
       <c r="I112" t="n">
-        <v>5</v>
+        <v>3020</v>
       </c>
       <c r="J112" t="n">
-        <v>39</v>
-      </c>
-      <c r="K112" t="n">
-        <v>5</v>
-      </c>
-      <c r="L112" t="n">
-        <v>96</v>
-      </c>
-      <c r="M112" t="n">
-        <v>3020</v>
-      </c>
-      <c r="N112" t="n">
         <v>3168</v>
       </c>
     </row>
@@ -5949,39 +4565,27 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>6</v>
+        <v>155</v>
       </c>
       <c r="D113" t="n">
-        <v>155</v>
+        <v>384</v>
       </c>
       <c r="E113" t="n">
-        <v>201</v>
+        <v>147</v>
       </c>
       <c r="F113" t="n">
-        <v>184</v>
+        <v>510</v>
       </c>
       <c r="G113" t="n">
-        <v>84</v>
+        <v>1</v>
       </c>
       <c r="H113" t="n">
-        <v>126</v>
+        <v>78</v>
       </c>
       <c r="I113" t="n">
-        <v>442</v>
+        <v>3</v>
       </c>
       <c r="J113" t="n">
-        <v>38</v>
-      </c>
-      <c r="K113" t="n">
-        <v>1</v>
-      </c>
-      <c r="L113" t="n">
-        <v>38</v>
-      </c>
-      <c r="M113" t="n">
-        <v>3</v>
-      </c>
-      <c r="N113" t="n">
         <v>1278</v>
       </c>
     </row>
@@ -6006,30 +4610,18 @@
         <v>0</v>
       </c>
       <c r="F114" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H114" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I114" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="J114" t="n">
-        <v>0</v>
-      </c>
-      <c r="K114" t="n">
-        <v>3</v>
-      </c>
-      <c r="L114" t="n">
-        <v>15</v>
-      </c>
-      <c r="M114" t="n">
-        <v>46</v>
-      </c>
-      <c r="N114" t="n">
         <v>66</v>
       </c>
     </row>
@@ -6048,10 +4640,10 @@
         <v>0</v>
       </c>
       <c r="D115" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E115" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F115" t="n">
         <v>3</v>
@@ -6060,24 +4652,12 @@
         <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="I115" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J115" t="n">
-        <v>0</v>
-      </c>
-      <c r="K115" t="n">
-        <v>0</v>
-      </c>
-      <c r="L115" t="n">
-        <v>3</v>
-      </c>
-      <c r="M115" t="n">
-        <v>3</v>
-      </c>
-      <c r="N115" t="n">
         <v>49</v>
       </c>
     </row>
@@ -6102,30 +4682,18 @@
         <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G116" t="n">
         <v>1</v>
       </c>
       <c r="H116" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I116" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="J116" t="n">
-        <v>0</v>
-      </c>
-      <c r="K116" t="n">
-        <v>1</v>
-      </c>
-      <c r="L116" t="n">
-        <v>8</v>
-      </c>
-      <c r="M116" t="n">
-        <v>19</v>
-      </c>
-      <c r="N116" t="n">
         <v>39</v>
       </c>
     </row>
@@ -6147,33 +4715,21 @@
         <v>0</v>
       </c>
       <c r="E117" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F117" t="n">
         <v>0</v>
       </c>
       <c r="G117" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I117" t="n">
         <v>0</v>
       </c>
       <c r="J117" t="n">
-        <v>0</v>
-      </c>
-      <c r="K117" t="n">
-        <v>0</v>
-      </c>
-      <c r="L117" t="n">
-        <v>0</v>
-      </c>
-      <c r="M117" t="n">
-        <v>0</v>
-      </c>
-      <c r="N117" t="n">
         <v>13</v>
       </c>
     </row>
@@ -6195,33 +4751,21 @@
         <v>0</v>
       </c>
       <c r="E118" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F118" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I118" t="n">
         <v>3</v>
       </c>
       <c r="J118" t="n">
-        <v>0</v>
-      </c>
-      <c r="K118" t="n">
-        <v>0</v>
-      </c>
-      <c r="L118" t="n">
-        <v>2</v>
-      </c>
-      <c r="M118" t="n">
-        <v>3</v>
-      </c>
-      <c r="N118" t="n">
         <v>10</v>
       </c>
     </row>
@@ -6246,30 +4790,18 @@
         <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
-        <v>0</v>
-      </c>
-      <c r="K119" t="n">
-        <v>0</v>
-      </c>
-      <c r="L119" t="n">
-        <v>3</v>
-      </c>
-      <c r="M119" t="n">
-        <v>1</v>
-      </c>
-      <c r="N119" t="n">
         <v>8</v>
       </c>
     </row>
@@ -6297,27 +4829,15 @@
         <v>0</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H120" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J120" t="n">
-        <v>0</v>
-      </c>
-      <c r="K120" t="n">
-        <v>1</v>
-      </c>
-      <c r="L120" t="n">
-        <v>3</v>
-      </c>
-      <c r="M120" t="n">
-        <v>1</v>
-      </c>
-      <c r="N120" t="n">
         <v>5</v>
       </c>
     </row>
@@ -6339,33 +4859,21 @@
         <v>0</v>
       </c>
       <c r="E121" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H121" t="n">
         <v>1</v>
       </c>
       <c r="I121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J121" t="n">
-        <v>0</v>
-      </c>
-      <c r="K121" t="n">
-        <v>0</v>
-      </c>
-      <c r="L121" t="n">
-        <v>1</v>
-      </c>
-      <c r="M121" t="n">
-        <v>0</v>
-      </c>
-      <c r="N121" t="n">
         <v>4</v>
       </c>
     </row>
@@ -6384,36 +4892,24 @@
         <v>0</v>
       </c>
       <c r="D122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E122" t="n">
         <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I122" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J122" t="n">
-        <v>0</v>
-      </c>
-      <c r="K122" t="n">
-        <v>0</v>
-      </c>
-      <c r="L122" t="n">
-        <v>1</v>
-      </c>
-      <c r="M122" t="n">
-        <v>2</v>
-      </c>
-      <c r="N122" t="n">
         <v>4</v>
       </c>
     </row>
@@ -6441,27 +4937,15 @@
         <v>0</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I123" t="n">
         <v>0</v>
       </c>
       <c r="J123" t="n">
-        <v>0</v>
-      </c>
-      <c r="K123" t="n">
-        <v>1</v>
-      </c>
-      <c r="L123" t="n">
-        <v>1</v>
-      </c>
-      <c r="M123" t="n">
-        <v>0</v>
-      </c>
-      <c r="N123" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6486,30 +4970,18 @@
         <v>0</v>
       </c>
       <c r="F124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J124" t="n">
-        <v>0</v>
-      </c>
-      <c r="K124" t="n">
-        <v>0</v>
-      </c>
-      <c r="L124" t="n">
-        <v>1</v>
-      </c>
-      <c r="M124" t="n">
-        <v>0</v>
-      </c>
-      <c r="N124" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6543,21 +5015,9 @@
         <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J125" t="n">
-        <v>0</v>
-      </c>
-      <c r="K125" t="n">
-        <v>0</v>
-      </c>
-      <c r="L125" t="n">
-        <v>0</v>
-      </c>
-      <c r="M125" t="n">
-        <v>2</v>
-      </c>
-      <c r="N125" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6582,7 +5042,7 @@
         <v>0</v>
       </c>
       <c r="F126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -6591,21 +5051,9 @@
         <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J126" t="n">
-        <v>0</v>
-      </c>
-      <c r="K126" t="n">
-        <v>0</v>
-      </c>
-      <c r="L126" t="n">
-        <v>0</v>
-      </c>
-      <c r="M126" t="n">
-        <v>0</v>
-      </c>
-      <c r="N126" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6627,7 +5075,7 @@
         <v>0</v>
       </c>
       <c r="E127" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F127" t="n">
         <v>0</v>
@@ -6636,24 +5084,12 @@
         <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I127" t="n">
         <v>0</v>
       </c>
       <c r="J127" t="n">
-        <v>0</v>
-      </c>
-      <c r="K127" t="n">
-        <v>0</v>
-      </c>
-      <c r="L127" t="n">
-        <v>0</v>
-      </c>
-      <c r="M127" t="n">
-        <v>0</v>
-      </c>
-      <c r="N127" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6687,21 +5123,9 @@
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J128" t="n">
-        <v>0</v>
-      </c>
-      <c r="K128" t="n">
-        <v>0</v>
-      </c>
-      <c r="L128" t="n">
-        <v>0</v>
-      </c>
-      <c r="M128" t="n">
-        <v>2</v>
-      </c>
-      <c r="N128" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6732,24 +5156,12 @@
         <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J129" t="n">
-        <v>0</v>
-      </c>
-      <c r="K129" t="n">
-        <v>0</v>
-      </c>
-      <c r="L129" t="n">
-        <v>1</v>
-      </c>
-      <c r="M129" t="n">
-        <v>1</v>
-      </c>
-      <c r="N129" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6774,7 +5186,7 @@
         <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -6786,18 +5198,6 @@
         <v>1</v>
       </c>
       <c r="J130" t="n">
-        <v>0</v>
-      </c>
-      <c r="K130" t="n">
-        <v>0</v>
-      </c>
-      <c r="L130" t="n">
-        <v>0</v>
-      </c>
-      <c r="M130" t="n">
-        <v>1</v>
-      </c>
-      <c r="N130" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6828,24 +5228,12 @@
         <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I131" t="n">
         <v>0</v>
       </c>
       <c r="J131" t="n">
-        <v>0</v>
-      </c>
-      <c r="K131" t="n">
-        <v>0</v>
-      </c>
-      <c r="L131" t="n">
-        <v>2</v>
-      </c>
-      <c r="M131" t="n">
-        <v>0</v>
-      </c>
-      <c r="N131" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6876,24 +5264,12 @@
         <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J132" t="n">
-        <v>0</v>
-      </c>
-      <c r="K132" t="n">
-        <v>0</v>
-      </c>
-      <c r="L132" t="n">
-        <v>1</v>
-      </c>
-      <c r="M132" t="n">
-        <v>1</v>
-      </c>
-      <c r="N132" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6924,24 +5300,12 @@
         <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J133" t="n">
-        <v>0</v>
-      </c>
-      <c r="K133" t="n">
-        <v>0</v>
-      </c>
-      <c r="L133" t="n">
-        <v>1</v>
-      </c>
-      <c r="M133" t="n">
-        <v>1</v>
-      </c>
-      <c r="N133" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6963,7 +5327,7 @@
         <v>0</v>
       </c>
       <c r="E134" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F134" t="n">
         <v>0</v>
@@ -6972,24 +5336,12 @@
         <v>0</v>
       </c>
       <c r="H134" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I134" t="n">
         <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>0</v>
-      </c>
-      <c r="K134" t="n">
-        <v>0</v>
-      </c>
-      <c r="L134" t="n">
-        <v>0</v>
-      </c>
-      <c r="M134" t="n">
-        <v>0</v>
-      </c>
-      <c r="N134" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7008,36 +5360,24 @@
         <v>0</v>
       </c>
       <c r="D135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E135" t="n">
         <v>0</v>
       </c>
       <c r="F135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I135" t="n">
         <v>0</v>
       </c>
       <c r="J135" t="n">
-        <v>0</v>
-      </c>
-      <c r="K135" t="n">
-        <v>0</v>
-      </c>
-      <c r="L135" t="n">
-        <v>1</v>
-      </c>
-      <c r="M135" t="n">
-        <v>0</v>
-      </c>
-      <c r="N135" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7059,7 +5399,7 @@
         <v>0</v>
       </c>
       <c r="E136" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F136" t="n">
         <v>0</v>
@@ -7068,24 +5408,12 @@
         <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I136" t="n">
         <v>0</v>
       </c>
       <c r="J136" t="n">
-        <v>0</v>
-      </c>
-      <c r="K136" t="n">
-        <v>0</v>
-      </c>
-      <c r="L136" t="n">
-        <v>0</v>
-      </c>
-      <c r="M136" t="n">
-        <v>0</v>
-      </c>
-      <c r="N136" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7116,24 +5444,12 @@
         <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I137" t="n">
         <v>0</v>
       </c>
       <c r="J137" t="n">
-        <v>0</v>
-      </c>
-      <c r="K137" t="n">
-        <v>0</v>
-      </c>
-      <c r="L137" t="n">
-        <v>1</v>
-      </c>
-      <c r="M137" t="n">
-        <v>0</v>
-      </c>
-      <c r="N137" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7167,21 +5483,9 @@
         <v>0</v>
       </c>
       <c r="I138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J138" t="n">
-        <v>0</v>
-      </c>
-      <c r="K138" t="n">
-        <v>0</v>
-      </c>
-      <c r="L138" t="n">
-        <v>0</v>
-      </c>
-      <c r="M138" t="n">
-        <v>1</v>
-      </c>
-      <c r="N138" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7206,7 +5510,7 @@
         <v>0</v>
       </c>
       <c r="F139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -7215,21 +5519,9 @@
         <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J139" t="n">
-        <v>0</v>
-      </c>
-      <c r="K139" t="n">
-        <v>0</v>
-      </c>
-      <c r="L139" t="n">
-        <v>0</v>
-      </c>
-      <c r="M139" t="n">
-        <v>0</v>
-      </c>
-      <c r="N139" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7263,21 +5555,9 @@
         <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J140" t="n">
-        <v>0</v>
-      </c>
-      <c r="K140" t="n">
-        <v>0</v>
-      </c>
-      <c r="L140" t="n">
-        <v>0</v>
-      </c>
-      <c r="M140" t="n">
-        <v>1</v>
-      </c>
-      <c r="N140" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7302,10 +5582,10 @@
         <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -7314,18 +5594,6 @@
         <v>0</v>
       </c>
       <c r="J141" t="n">
-        <v>0</v>
-      </c>
-      <c r="K141" t="n">
-        <v>0</v>
-      </c>
-      <c r="L141" t="n">
-        <v>0</v>
-      </c>
-      <c r="M141" t="n">
-        <v>0</v>
-      </c>
-      <c r="N141" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7356,24 +5624,12 @@
         <v>0</v>
       </c>
       <c r="H142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I142" t="n">
         <v>0</v>
       </c>
       <c r="J142" t="n">
-        <v>0</v>
-      </c>
-      <c r="K142" t="n">
-        <v>0</v>
-      </c>
-      <c r="L142" t="n">
-        <v>1</v>
-      </c>
-      <c r="M142" t="n">
-        <v>0</v>
-      </c>
-      <c r="N142" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7395,33 +5651,21 @@
         <v>0</v>
       </c>
       <c r="E143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
       </c>
       <c r="H143" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I143" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="J143" t="n">
-        <v>0</v>
-      </c>
-      <c r="K143" t="n">
-        <v>0</v>
-      </c>
-      <c r="L143" t="n">
-        <v>5</v>
-      </c>
-      <c r="M143" t="n">
-        <v>16</v>
-      </c>
-      <c r="N143" t="n">
         <v>23</v>
       </c>
     </row>
@@ -7437,39 +5681,27 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D144" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F144" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H144" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I144" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J144" t="n">
-        <v>0</v>
-      </c>
-      <c r="K144" t="n">
-        <v>1</v>
-      </c>
-      <c r="L144" t="n">
-        <v>2</v>
-      </c>
-      <c r="M144" t="n">
-        <v>1</v>
-      </c>
-      <c r="N144" t="n">
         <v>22</v>
       </c>
     </row>
@@ -7503,21 +5735,9 @@
         <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J145" t="n">
-        <v>0</v>
-      </c>
-      <c r="K145" t="n">
-        <v>0</v>
-      </c>
-      <c r="L145" t="n">
-        <v>0</v>
-      </c>
-      <c r="M145" t="n">
-        <v>1</v>
-      </c>
-      <c r="N145" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7551,21 +5771,9 @@
         <v>0</v>
       </c>
       <c r="I146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J146" t="n">
-        <v>0</v>
-      </c>
-      <c r="K146" t="n">
-        <v>0</v>
-      </c>
-      <c r="L146" t="n">
-        <v>0</v>
-      </c>
-      <c r="M146" t="n">
-        <v>1</v>
-      </c>
-      <c r="N146" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7596,24 +5804,12 @@
         <v>0</v>
       </c>
       <c r="H147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I147" t="n">
         <v>0</v>
       </c>
       <c r="J147" t="n">
-        <v>0</v>
-      </c>
-      <c r="K147" t="n">
-        <v>0</v>
-      </c>
-      <c r="L147" t="n">
-        <v>1</v>
-      </c>
-      <c r="M147" t="n">
-        <v>0</v>
-      </c>
-      <c r="N147" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7628,7 +5824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7679,26 +5875,6 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Tier_8_Tier 8</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Tier_9_Tier 9</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Tier_10_Tier 10</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Tier_11_Tier 11</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
           <t>Total</t>
         </is>
       </c>
@@ -7715,39 +5891,27 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>159</v>
       </c>
       <c r="D2" t="n">
-        <v>159</v>
+        <v>595</v>
       </c>
       <c r="E2" t="n">
-        <v>403</v>
+        <v>202</v>
       </c>
       <c r="F2" t="n">
-        <v>194</v>
+        <v>110</v>
       </c>
       <c r="G2" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>126</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
         <v>1072</v>
       </c>
     </row>
@@ -7766,36 +5930,24 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>393</v>
       </c>
       <c r="E3" t="n">
-        <v>202</v>
+        <v>147</v>
       </c>
       <c r="F3" t="n">
-        <v>192</v>
+        <v>73</v>
       </c>
       <c r="G3" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>126</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>2</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
         <v>619</v>
       </c>
     </row>
@@ -7811,39 +5963,27 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" t="n">
         <v>3</v>
       </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
       <c r="F4" t="n">
+        <v>517</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>44</v>
+      </c>
+      <c r="I4" t="n">
         <v>5</v>
       </c>
-      <c r="G4" t="n">
-        <v>31</v>
-      </c>
-      <c r="H4" t="n">
-        <v>36</v>
-      </c>
-      <c r="I4" t="n">
-        <v>449</v>
-      </c>
       <c r="J4" t="n">
-        <v>39</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M4" t="n">
-        <v>5</v>
-      </c>
-      <c r="N4" t="n">
         <v>579</v>
       </c>
     </row>
@@ -7859,39 +5999,27 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>324</v>
       </c>
       <c r="I5" t="n">
         <v>5</v>
       </c>
       <c r="J5" t="n">
-        <v>39</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>283</v>
-      </c>
-      <c r="M5" t="n">
-        <v>5</v>
-      </c>
-      <c r="N5" t="n">
         <v>337</v>
       </c>
     </row>
@@ -7910,36 +6038,24 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
         <v>97</v>
       </c>
     </row>
@@ -7958,36 +6074,24 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
         <v>54</v>
       </c>
     </row>
@@ -8006,36 +6110,24 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>36</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
         <v>41</v>
       </c>
     </row>
@@ -8054,36 +6146,24 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>3</v>
-      </c>
-      <c r="M9" t="n">
-        <v>2</v>
-      </c>
-      <c r="N9" t="n">
         <v>15</v>
       </c>
     </row>
@@ -8102,7 +6182,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -8117,21 +6197,9 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>6</v>
-      </c>
-      <c r="N10" t="n">
         <v>8</v>
       </c>
     </row>
@@ -8165,21 +6233,9 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>3</v>
-      </c>
-      <c r="N11" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8201,13 +6257,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -8216,18 +6272,6 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
         <v>2</v>
       </c>
     </row>
@@ -8261,21 +6305,9 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8290,7 +6322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8341,26 +6373,6 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Tier_8_Tier 8</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Tier_9_Tier 9</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Tier_10_Tier 10</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Tier_11_Tier 11</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
           <t>Total</t>
         </is>
       </c>
@@ -8380,36 +6392,24 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="E2" t="n">
-        <v>14</v>
+        <v>114</v>
       </c>
       <c r="F2" t="n">
-        <v>29</v>
+        <v>276</v>
       </c>
       <c r="G2" t="n">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="H2" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I2" t="n">
-        <v>226</v>
+        <v>196</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>15</v>
-      </c>
-      <c r="L2" t="n">
-        <v>87</v>
-      </c>
-      <c r="M2" t="n">
-        <v>196</v>
-      </c>
-      <c r="N2" t="n">
         <v>735</v>
       </c>
     </row>
@@ -8425,39 +6425,27 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>118</v>
       </c>
       <c r="E3" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F3" t="n">
-        <v>101</v>
+        <v>227</v>
       </c>
       <c r="G3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H3" t="n">
-        <v>60</v>
+        <v>98</v>
       </c>
       <c r="I3" t="n">
-        <v>184</v>
+        <v>98</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>13</v>
-      </c>
-      <c r="L3" t="n">
-        <v>96</v>
-      </c>
-      <c r="M3" t="n">
-        <v>98</v>
-      </c>
-      <c r="N3" t="n">
         <v>587</v>
       </c>
     </row>
@@ -8473,39 +6461,27 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="I4" t="n">
-        <v>86</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
-        <v>39</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>11</v>
-      </c>
-      <c r="M4" t="n">
-        <v>5</v>
-      </c>
-      <c r="N4" t="n">
         <v>144</v>
       </c>
     </row>
@@ -8521,39 +6497,27 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="I5" t="n">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>6</v>
-      </c>
-      <c r="L5" t="n">
-        <v>20</v>
-      </c>
-      <c r="M5" t="n">
-        <v>13</v>
-      </c>
-      <c r="N5" t="n">
         <v>102</v>
       </c>
     </row>
@@ -8572,36 +6536,24 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="I6" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>18</v>
-      </c>
-      <c r="M6" t="n">
-        <v>43</v>
-      </c>
-      <c r="N6" t="n">
         <v>93</v>
       </c>
     </row>
@@ -8620,36 +6572,24 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I7" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4</v>
-      </c>
-      <c r="L7" t="n">
-        <v>13</v>
-      </c>
-      <c r="M7" t="n">
-        <v>30</v>
-      </c>
-      <c r="N7" t="n">
         <v>90</v>
       </c>
     </row>
@@ -8674,30 +6614,18 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I8" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>12</v>
-      </c>
-      <c r="M8" t="n">
-        <v>32</v>
-      </c>
-      <c r="N8" t="n">
         <v>55</v>
       </c>
     </row>
@@ -8716,36 +6644,24 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I9" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3</v>
-      </c>
-      <c r="L9" t="n">
-        <v>7</v>
-      </c>
-      <c r="M9" t="n">
-        <v>7</v>
-      </c>
-      <c r="N9" t="n">
         <v>39</v>
       </c>
     </row>
@@ -8770,30 +6686,18 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>3</v>
-      </c>
-      <c r="M10" t="n">
-        <v>8</v>
-      </c>
-      <c r="N10" t="n">
         <v>27</v>
       </c>
     </row>
@@ -8818,30 +6722,18 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>10</v>
-      </c>
-      <c r="M11" t="n">
-        <v>7</v>
-      </c>
-      <c r="N11" t="n">
         <v>20</v>
       </c>
     </row>
@@ -8857,39 +6749,27 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>2</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
         <v>15</v>
       </c>
     </row>
@@ -8914,30 +6794,18 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>3</v>
-      </c>
-      <c r="M13" t="n">
-        <v>8</v>
-      </c>
-      <c r="N13" t="n">
         <v>14</v>
       </c>
     </row>
@@ -8962,30 +6830,18 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>5</v>
-      </c>
-      <c r="M14" t="n">
-        <v>4</v>
-      </c>
-      <c r="N14" t="n">
         <v>11</v>
       </c>
     </row>
@@ -9010,30 +6866,18 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>3</v>
-      </c>
-      <c r="M15" t="n">
-        <v>3</v>
-      </c>
-      <c r="N15" t="n">
         <v>7</v>
       </c>
     </row>
@@ -9052,13 +6896,13 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -9067,21 +6911,9 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
         <v>7</v>
       </c>
     </row>
@@ -9106,7 +6938,7 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -9115,21 +6947,9 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
         <v>6</v>
       </c>
     </row>
@@ -9154,30 +6974,18 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>3</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
         <v>6</v>
       </c>
     </row>
@@ -9202,30 +7010,18 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>3</v>
-      </c>
-      <c r="M19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N19" t="n">
         <v>6</v>
       </c>
     </row>
@@ -9253,27 +7049,15 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1</v>
-      </c>
-      <c r="M20" t="n">
-        <v>4</v>
-      </c>
-      <c r="N20" t="n">
         <v>6</v>
       </c>
     </row>
@@ -9289,7 +7073,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -9298,7 +7082,7 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -9310,18 +7094,6 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
         <v>2</v>
       </c>
     </row>
@@ -9340,7 +7112,7 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -9355,21 +7127,9 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
         <v>2</v>
       </c>
     </row>
@@ -9385,7 +7145,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
         <v>1</v>
@@ -9394,7 +7154,7 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -9406,18 +7166,6 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
         <v>2</v>
       </c>
     </row>
@@ -9442,10 +7190,10 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -9454,18 +7202,6 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
         <v>2</v>
       </c>
     </row>
@@ -9499,21 +7235,9 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1</v>
-      </c>
-      <c r="N25" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9538,7 +7262,7 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -9547,21 +7271,9 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9586,7 +7298,7 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -9595,21 +7307,9 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9643,21 +7343,9 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1</v>
-      </c>
-      <c r="N28" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9691,21 +7379,9 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1</v>
-      </c>
-      <c r="N29" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9739,21 +7415,9 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1</v>
-      </c>
-      <c r="N30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9787,21 +7451,9 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1</v>
-      </c>
-      <c r="N31" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9826,7 +7478,7 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -9835,21 +7487,9 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9864,7 +7504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9880,45 +7520,40 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Tier_1_Spores</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Tier_2_Germinated</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Tier_3_Microcolonies</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Tier_4_Small colonies</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Tier_5_WT-like</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>Tier_6_Tier 6</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Tier_7_Tier 7</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Tier_9_Tier 9</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Tier_10_Tier 10</t>
-        </is>
-      </c>
       <c r="J1" t="inlineStr">
-        <is>
-          <t>Tier_11_Tier 11</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -9942,24 +7577,21 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="J2" t="n">
-        <v>16</v>
-      </c>
-      <c r="K2" t="n">
         <v>23</v>
       </c>
     </row>
@@ -9978,27 +7610,24 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
         <v>22</v>
       </c>
     </row>
@@ -10032,12 +7661,9 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10071,12 +7697,9 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10107,15 +7730,12 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10146,22 +7766,22 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Tier_4_Small colonies</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Tier_5_WT-like</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Tier_6_Tier 6</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Tier_7_Tier 7</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Tier_9_Tier 9</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Tier_10_Tier 10</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Tier_11_Tier 11</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -10424,7 +8044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10475,21 +8095,6 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Tier_9_Tier 9</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Tier_10_Tier 10</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Tier_11_Tier 11</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
           <t>Total</t>
         </is>
       </c>
@@ -10506,36 +8111,27 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>110</v>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>186</v>
       </c>
       <c r="G2" t="n">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="H2" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="I2" t="n">
-        <v>169</v>
+        <v>225</v>
       </c>
       <c r="J2" t="n">
-        <v>13</v>
-      </c>
-      <c r="K2" t="n">
-        <v>74</v>
-      </c>
-      <c r="L2" t="n">
-        <v>225</v>
-      </c>
-      <c r="M2" t="n">
         <v>619</v>
       </c>
     </row>
@@ -10554,33 +8150,24 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -10611,21 +8198,12 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -10656,21 +8234,12 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10689,7 +8258,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -10704,18 +8273,9 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10746,21 +8306,12 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10785,7 +8336,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -10794,18 +8345,9 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10821,36 +8363,27 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F9" t="n">
+        <v>22</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="n">
         <v>6</v>
       </c>
-      <c r="G9" t="n">
-        <v>22</v>
-      </c>
-      <c r="H9" t="n">
-        <v>17</v>
-      </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>6</v>
-      </c>
-      <c r="L9" t="n">
-        <v>11</v>
-      </c>
-      <c r="M9" t="n">
         <v>72</v>
       </c>
     </row>
@@ -10866,36 +8399,27 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3</v>
-      </c>
-      <c r="L10" t="n">
-        <v>9</v>
-      </c>
-      <c r="M10" t="n">
         <v>65</v>
       </c>
     </row>
@@ -10920,27 +8444,18 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L11" t="n">
-        <v>4</v>
-      </c>
-      <c r="M11" t="n">
         <v>14</v>
       </c>
     </row>
@@ -10959,13 +8474,13 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -10974,18 +8489,9 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>5</v>
-      </c>
-      <c r="M12" t="n">
         <v>7</v>
       </c>
     </row>
@@ -11007,30 +8513,21 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
         <v>7</v>
       </c>
     </row>
@@ -11061,21 +8558,12 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11109,18 +8597,9 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11145,10 +8624,10 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -11157,15 +8636,6 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11199,18 +8669,9 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11229,33 +8690,24 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="E18" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="G18" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="I18" t="n">
-        <v>87</v>
+        <v>33</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>13</v>
-      </c>
-      <c r="L18" t="n">
-        <v>33</v>
-      </c>
-      <c r="M18" t="n">
         <v>251</v>
       </c>
     </row>
@@ -11277,30 +8729,21 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
         <v>74</v>
       </c>
     </row>
@@ -11319,33 +8762,24 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2</v>
-      </c>
-      <c r="L20" t="n">
-        <v>9</v>
-      </c>
-      <c r="M20" t="n">
         <v>19</v>
       </c>
     </row>
@@ -11367,30 +8801,21 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
         <v>15</v>
       </c>
     </row>
@@ -11415,27 +8840,18 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>3</v>
-      </c>
-      <c r="M22" t="n">
         <v>5</v>
       </c>
     </row>
@@ -11466,21 +8882,12 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>3</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" t="n">
         <v>4</v>
       </c>
     </row>
@@ -11514,18 +8921,9 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>2</v>
-      </c>
-      <c r="M24" t="n">
         <v>2</v>
       </c>
     </row>
@@ -11559,18 +8957,9 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11585,7 +8974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N51"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11636,26 +9025,6 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Tier_8_Tier 8</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Tier_9_Tier 9</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Tier_10_Tier 10</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Tier_11_Tier 11</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
           <t>Total</t>
         </is>
       </c>
@@ -11672,39 +9041,27 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>159</v>
       </c>
       <c r="D2" t="n">
-        <v>159</v>
+        <v>595</v>
       </c>
       <c r="E2" t="n">
-        <v>403</v>
+        <v>202</v>
       </c>
       <c r="F2" t="n">
-        <v>194</v>
+        <v>110</v>
       </c>
       <c r="G2" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>126</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
         <v>1072</v>
       </c>
     </row>
@@ -11720,39 +9077,27 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" t="n">
         <v>3</v>
       </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
       <c r="F3" t="n">
+        <v>517</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>44</v>
+      </c>
+      <c r="I3" t="n">
         <v>5</v>
       </c>
-      <c r="G3" t="n">
-        <v>31</v>
-      </c>
-      <c r="H3" t="n">
-        <v>36</v>
-      </c>
-      <c r="I3" t="n">
-        <v>449</v>
-      </c>
       <c r="J3" t="n">
-        <v>39</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>5</v>
-      </c>
-      <c r="M3" t="n">
-        <v>5</v>
-      </c>
-      <c r="N3" t="n">
         <v>579</v>
       </c>
     </row>
@@ -11771,36 +9116,24 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N4" t="n">
         <v>15</v>
       </c>
     </row>
@@ -11834,21 +9167,9 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>3</v>
-      </c>
-      <c r="N5" t="n">
         <v>3</v>
       </c>
     </row>
@@ -11870,13 +9191,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -11885,18 +9206,6 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
         <v>2</v>
       </c>
     </row>
@@ -11930,21 +9239,9 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11960,39 +9257,27 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>110</v>
       </c>
       <c r="F8" t="n">
-        <v>7</v>
+        <v>186</v>
       </c>
       <c r="G8" t="n">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="H8" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="I8" t="n">
-        <v>169</v>
+        <v>225</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>13</v>
-      </c>
-      <c r="L8" t="n">
-        <v>74</v>
-      </c>
-      <c r="M8" t="n">
-        <v>225</v>
-      </c>
-      <c r="N8" t="n">
         <v>619</v>
       </c>
     </row>
@@ -12023,24 +9308,12 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
         <v>2</v>
       </c>
     </row>
@@ -12065,7 +9338,7 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -12074,21 +9347,9 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12113,30 +9374,18 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M11" t="n">
-        <v>4</v>
-      </c>
-      <c r="N11" t="n">
         <v>14</v>
       </c>
     </row>
@@ -12155,13 +9404,13 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -12170,21 +9419,9 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>5</v>
-      </c>
-      <c r="N12" t="n">
         <v>7</v>
       </c>
     </row>
@@ -12215,24 +9452,12 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12257,10 +9482,10 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -12269,18 +9494,6 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12314,21 +9527,9 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12344,39 +9545,27 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="I16" t="n">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>6</v>
-      </c>
-      <c r="L16" t="n">
-        <v>20</v>
-      </c>
-      <c r="M16" t="n">
-        <v>13</v>
-      </c>
-      <c r="N16" t="n">
         <v>102</v>
       </c>
     </row>
@@ -12395,36 +9584,24 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H17" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I17" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>4</v>
-      </c>
-      <c r="L17" t="n">
-        <v>13</v>
-      </c>
-      <c r="M17" t="n">
-        <v>30</v>
-      </c>
-      <c r="N17" t="n">
         <v>90</v>
       </c>
     </row>
@@ -12443,36 +9620,24 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I18" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L18" t="n">
-        <v>7</v>
-      </c>
-      <c r="M18" t="n">
-        <v>7</v>
-      </c>
-      <c r="N18" t="n">
         <v>39</v>
       </c>
     </row>
@@ -12497,30 +9662,18 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>10</v>
-      </c>
-      <c r="M19" t="n">
-        <v>7</v>
-      </c>
-      <c r="N19" t="n">
         <v>20</v>
       </c>
     </row>
@@ -12545,30 +9698,18 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" t="n">
-        <v>3</v>
-      </c>
-      <c r="M20" t="n">
-        <v>8</v>
-      </c>
-      <c r="N20" t="n">
         <v>14</v>
       </c>
     </row>
@@ -12593,30 +9734,18 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>5</v>
-      </c>
-      <c r="M21" t="n">
-        <v>4</v>
-      </c>
-      <c r="N21" t="n">
         <v>11</v>
       </c>
     </row>
@@ -12641,30 +9770,18 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>3</v>
-      </c>
-      <c r="M22" t="n">
-        <v>3</v>
-      </c>
-      <c r="N22" t="n">
         <v>7</v>
       </c>
     </row>
@@ -12689,30 +9806,18 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>3</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
         <v>6</v>
       </c>
     </row>
@@ -12737,30 +9842,18 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>3</v>
-      </c>
-      <c r="M24" t="n">
-        <v>2</v>
-      </c>
-      <c r="N24" t="n">
         <v>6</v>
       </c>
     </row>
@@ -12788,27 +9881,15 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" t="n">
-        <v>4</v>
-      </c>
-      <c r="N25" t="n">
         <v>6</v>
       </c>
     </row>
@@ -12827,7 +9908,7 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -12842,21 +9923,9 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
         <v>2</v>
       </c>
     </row>
@@ -12881,10 +9950,10 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -12893,18 +9962,6 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
         <v>2</v>
       </c>
     </row>
@@ -12923,13 +9980,13 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -12941,18 +9998,6 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12977,7 +10022,7 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -12986,21 +10031,9 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13025,7 +10058,7 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -13034,21 +10067,9 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13073,7 +10094,7 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -13082,21 +10103,9 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13130,21 +10139,9 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>1</v>
-      </c>
-      <c r="N32" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13178,21 +10175,9 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1</v>
-      </c>
-      <c r="N33" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13226,21 +10211,9 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>1</v>
-      </c>
-      <c r="N34" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13274,21 +10247,9 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>1</v>
-      </c>
-      <c r="N35" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13313,7 +10274,7 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -13322,21 +10283,9 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13361,30 +10310,18 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>2</v>
-      </c>
-      <c r="M37" t="n">
-        <v>2</v>
-      </c>
-      <c r="N37" t="n">
         <v>5</v>
       </c>
     </row>
@@ -13415,24 +10352,12 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
-        <v>4</v>
-      </c>
-      <c r="M38" t="n">
-        <v>1</v>
-      </c>
-      <c r="N38" t="n">
         <v>5</v>
       </c>
     </row>
@@ -13457,7 +10382,7 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -13466,21 +10391,9 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
         <v>4</v>
       </c>
     </row>
@@ -13511,24 +10424,12 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
-        <v>2</v>
-      </c>
-      <c r="M40" t="n">
-        <v>2</v>
-      </c>
-      <c r="N40" t="n">
         <v>4</v>
       </c>
     </row>
@@ -13562,21 +10463,9 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>4</v>
-      </c>
-      <c r="N41" t="n">
         <v>4</v>
       </c>
     </row>
@@ -13601,30 +10490,18 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
         <v>1</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="n">
-        <v>1</v>
-      </c>
-      <c r="M42" t="n">
-        <v>1</v>
-      </c>
-      <c r="N42" t="n">
         <v>3</v>
       </c>
     </row>
@@ -13655,24 +10532,12 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
-        <v>2</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="n">
         <v>2</v>
       </c>
     </row>
@@ -13703,24 +10568,12 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>2</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
         <v>2</v>
       </c>
     </row>
@@ -13754,21 +10607,9 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>2</v>
-      </c>
-      <c r="N45" t="n">
         <v>2</v>
       </c>
     </row>
@@ -13802,21 +10643,9 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>2</v>
-      </c>
-      <c r="N46" t="n">
         <v>2</v>
       </c>
     </row>
@@ -13847,24 +10676,12 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
-        <v>1</v>
-      </c>
-      <c r="M47" t="n">
-        <v>1</v>
-      </c>
-      <c r="N47" t="n">
         <v>2</v>
       </c>
     </row>
@@ -13898,21 +10715,9 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>1</v>
-      </c>
-      <c r="N48" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13946,21 +10751,9 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>1</v>
-      </c>
-      <c r="N49" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13985,7 +10778,7 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -13994,21 +10787,9 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14042,21 +10823,9 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>1</v>
-      </c>
-      <c r="N51" t="n">
         <v>1</v>
       </c>
     </row>
